--- a/MedicalSuiteNova/wwwroot/formats/Pacientes_importacion.xlsx
+++ b/MedicalSuiteNova/wwwroot/formats/Pacientes_importacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\clinical-api\MedicalSuiteNova\wwwroot\formats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\api\MedicalSuiteNova\MedicalSuiteNova\MedicalSuiteNova\wwwroot\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE5CB2B-EEAF-456B-B712-00BF8007EF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9D75CA-13E5-454E-BCE8-8E1A228A8913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{52DB1DEC-0278-4875-B133-201483EA5FF2}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="38700" windowHeight="15345" xr2:uid="{52DB1DEC-0278-4875-B133-201483EA5FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Nombre</t>
   </si>
@@ -33,35 +33,20 @@
     <t>Apellido</t>
   </si>
   <si>
-    <t>Edad</t>
-  </si>
-  <si>
     <t>Telefono</t>
   </si>
   <si>
-    <t>ert</t>
+    <t>Email</t>
   </si>
   <si>
-    <t>ertert</t>
-  </si>
-  <si>
-    <t>Alex</t>
-  </si>
-  <si>
-    <t>Campos</t>
-  </si>
-  <si>
-    <t>Fabio</t>
-  </si>
-  <si>
-    <t>Email</t>
+    <t xml:space="preserve">Identificación </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,13 +54,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -87,13 +91,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -406,57 +413,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D0E58F-44C3-4CFD-B01B-8035D71ECD44}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.90625" customWidth="1"/>
-    <col min="2" max="2" width="31.90625" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="15.7265625" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="40.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
